--- a/datos/valido_con_metadatos.xlsx
+++ b/datos/valido_con_metadatos.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="datos_IV" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="resumen" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -495,10 +496,10 @@
         <v>-1</v>
       </c>
       <c r="B6" t="n">
-        <v>-0.0008339060523306628</v>
+        <v>-0.0007056319172174438</v>
       </c>
       <c r="C6" t="n">
-        <v>0.525994743596507</v>
+        <v>0.7130706761946477</v>
       </c>
       <c r="D6" t="inlineStr"/>
     </row>
@@ -507,10 +508,10 @@
         <v>-0.9591836734693877</v>
       </c>
       <c r="B7" t="n">
-        <v>-0.0007862285812893863</v>
+        <v>-0.0008102184027581541</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1246537168893784</v>
+        <v>0.7314384742590251</v>
       </c>
       <c r="D7" t="inlineStr"/>
     </row>
@@ -519,10 +520,10 @@
         <v>-0.9183673469387755</v>
       </c>
       <c r="B8" t="n">
-        <v>-0.0007889208389662268</v>
+        <v>-0.0007606720819066132</v>
       </c>
       <c r="C8" t="n">
-        <v>0.4245400517758303</v>
+        <v>0.6992933040051039</v>
       </c>
       <c r="D8" t="inlineStr"/>
     </row>
@@ -531,10 +532,10 @@
         <v>-0.8775510204081632</v>
       </c>
       <c r="B9" t="n">
-        <v>-0.0007980143268133934</v>
+        <v>-0.0008317804595584452</v>
       </c>
       <c r="C9" t="n">
-        <v>0.4849170175005559</v>
+        <v>0.421132510562599</v>
       </c>
       <c r="D9" t="inlineStr"/>
     </row>
@@ -543,10 +544,10 @@
         <v>-0.8367346938775511</v>
       </c>
       <c r="B10" t="n">
-        <v>-0.0007737745370863507</v>
+        <v>-0.00092800624330186</v>
       </c>
       <c r="C10" t="n">
-        <v>0.975693064092093</v>
+        <v>0.9801075363331501</v>
       </c>
       <c r="D10" t="inlineStr"/>
     </row>
@@ -555,10 +556,10 @@
         <v>-0.7959183673469388</v>
       </c>
       <c r="B11" t="n">
-        <v>-0.0008159035184855859</v>
+        <v>-0.0008344619230068233</v>
       </c>
       <c r="C11" t="n">
-        <v>0.796216721879618</v>
+        <v>0.190627659720545</v>
       </c>
       <c r="D11" t="inlineStr"/>
     </row>
@@ -567,10 +568,10 @@
         <v>-0.7551020408163265</v>
       </c>
       <c r="B12" t="n">
-        <v>-0.0006816601162970099</v>
+        <v>-0.0008189548365732984</v>
       </c>
       <c r="C12" t="n">
-        <v>0.1050785653533025</v>
+        <v>0.3952075251163591</v>
       </c>
       <c r="D12" t="inlineStr"/>
     </row>
@@ -579,10 +580,10 @@
         <v>-0.7142857142857143</v>
       </c>
       <c r="B13" t="n">
-        <v>-0.0008629718805590371</v>
+        <v>-0.0008879904676547991</v>
       </c>
       <c r="C13" t="n">
-        <v>0.02449112306601664</v>
+        <v>0.5733217455838677</v>
       </c>
       <c r="D13" t="inlineStr"/>
     </row>
@@ -591,10 +592,10 @@
         <v>-0.6734693877551021</v>
       </c>
       <c r="B14" t="n">
-        <v>-0.0007493530414128639</v>
+        <v>-0.0007558890252109872</v>
       </c>
       <c r="C14" t="n">
-        <v>0.05480570952123476</v>
+        <v>0.597843226651391</v>
       </c>
       <c r="D14" t="inlineStr"/>
     </row>
@@ -603,10 +604,10 @@
         <v>-0.6326530612244898</v>
       </c>
       <c r="B15" t="n">
-        <v>-0.0008685665001919864</v>
+        <v>-0.0008980746898849185</v>
       </c>
       <c r="C15" t="n">
-        <v>0.6954014891843724</v>
+        <v>0.6253896586987483</v>
       </c>
       <c r="D15" t="inlineStr"/>
     </row>
@@ -615,10 +616,10 @@
         <v>-0.5918367346938775</v>
       </c>
       <c r="B16" t="n">
-        <v>-0.0007756237245050198</v>
+        <v>-0.00083735618611989</v>
       </c>
       <c r="C16" t="n">
-        <v>0.7299096242617737</v>
+        <v>0.09966997829063085</v>
       </c>
       <c r="D16" t="inlineStr"/>
     </row>
@@ -627,10 +628,10 @@
         <v>-0.5510204081632654</v>
       </c>
       <c r="B17" t="n">
-        <v>-0.0008013780427157482</v>
+        <v>-0.0006984130203875136</v>
       </c>
       <c r="C17" t="n">
-        <v>0.03561986482360002</v>
+        <v>0.4222969785940905</v>
       </c>
       <c r="D17" t="inlineStr"/>
     </row>
@@ -639,10 +640,10 @@
         <v>-0.5102040816326531</v>
       </c>
       <c r="B18" t="n">
-        <v>-0.0008131576104516193</v>
+        <v>-0.0007036665475842485</v>
       </c>
       <c r="C18" t="n">
-        <v>0.759778664803399</v>
+        <v>0.3189478073316205</v>
       </c>
       <c r="D18" t="inlineStr"/>
     </row>
@@ -651,10 +652,10 @@
         <v>-0.4693877551020409</v>
       </c>
       <c r="B19" t="n">
-        <v>-0.0008881376397187578</v>
+        <v>-0.000821772168422871</v>
       </c>
       <c r="C19" t="n">
-        <v>0.2040805617518349</v>
+        <v>0.5904898397077615</v>
       </c>
       <c r="D19" t="inlineStr"/>
     </row>
@@ -663,10 +664,10 @@
         <v>-0.4285714285714286</v>
       </c>
       <c r="B20" t="n">
-        <v>-0.0008238948629097372</v>
+        <v>-0.0009107423894526014</v>
       </c>
       <c r="C20" t="n">
-        <v>0.2946464897594812</v>
+        <v>0.4177848509501629</v>
       </c>
       <c r="D20" t="inlineStr"/>
     </row>
@@ -675,10 +676,10 @@
         <v>-0.3877551020408164</v>
       </c>
       <c r="B21" t="n">
-        <v>-0.0008556200667838575</v>
+        <v>-0.0008205921102243178</v>
       </c>
       <c r="C21" t="n">
-        <v>0.6117797623773795</v>
+        <v>0.2669124964901746</v>
       </c>
       <c r="D21" t="inlineStr"/>
     </row>
@@ -687,10 +688,10 @@
         <v>-0.3469387755102041</v>
       </c>
       <c r="B22" t="n">
-        <v>-0.00081905529051847</v>
+        <v>-0.0006701204880741187</v>
       </c>
       <c r="C22" t="n">
-        <v>0.8771855976649219</v>
+        <v>0.2824648493021318</v>
       </c>
       <c r="D22" t="inlineStr"/>
     </row>
@@ -699,10 +700,10 @@
         <v>-0.3061224489795918</v>
       </c>
       <c r="B23" t="n">
-        <v>-0.0007833540384968991</v>
+        <v>-0.0008189819258430055</v>
       </c>
       <c r="C23" t="n">
-        <v>0.1362654334319823</v>
+        <v>0.8469304519300892</v>
       </c>
       <c r="D23" t="inlineStr"/>
     </row>
@@ -711,10 +712,10 @@
         <v>-0.2653061224489797</v>
       </c>
       <c r="B24" t="n">
-        <v>-0.0007239748209395903</v>
+        <v>-0.0006689771387611338</v>
       </c>
       <c r="C24" t="n">
-        <v>0.7337508246618638</v>
+        <v>0.5022845755670677</v>
       </c>
       <c r="D24" t="inlineStr"/>
     </row>
@@ -723,10 +724,10 @@
         <v>-0.2244897959183674</v>
       </c>
       <c r="B25" t="n">
-        <v>-0.0006441570412915624</v>
+        <v>-0.0007152264370050051</v>
       </c>
       <c r="C25" t="n">
-        <v>0.2048703487445833</v>
+        <v>0.3015879132333809</v>
       </c>
       <c r="D25" t="inlineStr"/>
     </row>
@@ -735,10 +736,10 @@
         <v>-0.1836734693877552</v>
       </c>
       <c r="B26" t="n">
-        <v>-0.0007083597184820652</v>
+        <v>-0.0005791613576086947</v>
       </c>
       <c r="C26" t="n">
-        <v>0.9287356392047186</v>
+        <v>0.7756038172360219</v>
       </c>
       <c r="D26" t="inlineStr"/>
     </row>
@@ -747,10 +748,10 @@
         <v>-0.1428571428571429</v>
       </c>
       <c r="B27" t="n">
-        <v>-0.0005994618948897211</v>
+        <v>-0.0004959547899229805</v>
       </c>
       <c r="C27" t="n">
-        <v>0.1552714867136733</v>
+        <v>0.4852954799401713</v>
       </c>
       <c r="D27" t="inlineStr"/>
     </row>
@@ -759,10 +760,10 @@
         <v>-0.1020408163265307</v>
       </c>
       <c r="B28" t="n">
-        <v>-0.0005090425823822902</v>
+        <v>-0.0005659549030819632</v>
       </c>
       <c r="C28" t="n">
-        <v>0.9950390869366045</v>
+        <v>0.2991958146516529</v>
       </c>
       <c r="D28" t="inlineStr"/>
     </row>
@@ -771,10 +772,10 @@
         <v>-0.06122448979591844</v>
       </c>
       <c r="B29" t="n">
-        <v>-0.0003246117486493671</v>
+        <v>-0.0002166654797018099</v>
       </c>
       <c r="C29" t="n">
-        <v>0.3441569700528716</v>
+        <v>0.5148126758504772</v>
       </c>
       <c r="D29" t="inlineStr"/>
     </row>
@@ -783,10 +784,10 @@
         <v>-0.02040816326530615</v>
       </c>
       <c r="B30" t="n">
-        <v>-0.0002238041350081134</v>
+        <v>-0.0002868106125021236</v>
       </c>
       <c r="C30" t="n">
-        <v>0.5142204194339993</v>
+        <v>0.2969576512456843</v>
       </c>
       <c r="D30" t="inlineStr"/>
     </row>
@@ -795,10 +796,10 @@
         <v>0.02040816326530615</v>
       </c>
       <c r="B31" t="n">
-        <v>0.0002474592137565727</v>
+        <v>0.0002070816401277807</v>
       </c>
       <c r="C31" t="n">
-        <v>0.3055191862159725</v>
+        <v>0.0166094816479484</v>
       </c>
       <c r="D31" t="inlineStr"/>
     </row>
@@ -807,10 +808,10 @@
         <v>0.06122448979591821</v>
       </c>
       <c r="B32" t="n">
-        <v>0.0004850663580294249</v>
+        <v>0.0007956324009088742</v>
       </c>
       <c r="C32" t="n">
-        <v>0.6397939519259762</v>
+        <v>0.9448448380117187</v>
       </c>
       <c r="D32" t="inlineStr"/>
     </row>
@@ -819,10 +820,10 @@
         <v>0.1020408163265305</v>
       </c>
       <c r="B33" t="n">
-        <v>0.001350084319186077</v>
+        <v>0.001426147934492343</v>
       </c>
       <c r="C33" t="n">
-        <v>0.2643334080592243</v>
+        <v>0.07892935484533192</v>
       </c>
       <c r="D33" t="inlineStr"/>
     </row>
@@ -831,10 +832,10 @@
         <v>0.1428571428571428</v>
       </c>
       <c r="B34" t="n">
-        <v>0.0023702401151984</v>
+        <v>0.002571277815063434</v>
       </c>
       <c r="C34" t="n">
-        <v>0.9914495762120158</v>
+        <v>0.5703202004458304</v>
       </c>
       <c r="D34" t="inlineStr"/>
     </row>
@@ -843,10 +844,10 @@
         <v>0.1836734693877551</v>
       </c>
       <c r="B35" t="n">
-        <v>0.004141903111347968</v>
+        <v>0.00430074992223484</v>
       </c>
       <c r="C35" t="n">
-        <v>0.2201564693252783</v>
+        <v>0.2621873176544667</v>
       </c>
       <c r="D35" t="inlineStr"/>
     </row>
@@ -855,10 +856,10 @@
         <v>0.2244897959183672</v>
       </c>
       <c r="B36" t="n">
-        <v>0.006791312155881143</v>
+        <v>0.006678439838576448</v>
       </c>
       <c r="C36" t="n">
-        <v>0.1237717521213391</v>
+        <v>0.2971026679477532</v>
       </c>
       <c r="D36" t="inlineStr"/>
     </row>
@@ -867,10 +868,10 @@
         <v>0.2653061224489794</v>
       </c>
       <c r="B37" t="n">
-        <v>0.01058481687069146</v>
+        <v>0.01060120486221794</v>
       </c>
       <c r="C37" t="n">
-        <v>0.5962986242933376</v>
+        <v>0.417163102651251</v>
       </c>
       <c r="D37" t="inlineStr"/>
     </row>
@@ -879,10 +880,10 @@
         <v>0.3061224489795917</v>
       </c>
       <c r="B38" t="n">
-        <v>0.01624646451525542</v>
+        <v>0.01626610122036994</v>
       </c>
       <c r="C38" t="n">
-        <v>0.2893864591416576</v>
+        <v>0.1991538066089307</v>
       </c>
       <c r="D38" t="inlineStr"/>
     </row>
@@ -891,10 +892,10 @@
         <v>0.346938775510204</v>
       </c>
       <c r="B39" t="n">
-        <v>0.02494215301952105</v>
+        <v>0.02495471783342904</v>
       </c>
       <c r="C39" t="n">
-        <v>0.82860913925771</v>
+        <v>0.05042422668989555</v>
       </c>
       <c r="D39" t="inlineStr"/>
     </row>
@@ -903,10 +904,10 @@
         <v>0.3877551020408163</v>
       </c>
       <c r="B40" t="n">
-        <v>0.03793986574943767</v>
+        <v>0.03775928243762504</v>
       </c>
       <c r="C40" t="n">
-        <v>0.8104251708248622</v>
+        <v>0.7628344246411092</v>
       </c>
       <c r="D40" t="inlineStr"/>
     </row>
@@ -915,10 +916,10 @@
         <v>0.4285714285714284</v>
       </c>
       <c r="B41" t="n">
-        <v>0.05735146745609516</v>
+        <v>0.05721301688484279</v>
       </c>
       <c r="C41" t="n">
-        <v>0.4186702984207182</v>
+        <v>0.144554099492636</v>
       </c>
       <c r="D41" t="inlineStr"/>
     </row>
@@ -927,10 +928,10 @@
         <v>0.4693877551020407</v>
       </c>
       <c r="B42" t="n">
-        <v>0.08660704099276695</v>
+        <v>0.08667084460902992</v>
       </c>
       <c r="C42" t="n">
-        <v>0.4671487567017608</v>
+        <v>0.5488211136993367</v>
       </c>
       <c r="D42" t="inlineStr"/>
     </row>
@@ -939,10 +940,10 @@
         <v>0.510204081632653</v>
       </c>
       <c r="B43" t="n">
-        <v>0.1306566689575019</v>
+        <v>0.1307566885370252</v>
       </c>
       <c r="C43" t="n">
-        <v>0.4039119676070279</v>
+        <v>0.7433672347454496</v>
       </c>
       <c r="D43" t="inlineStr"/>
     </row>
@@ -951,10 +952,10 @@
         <v>0.5510204081632653</v>
       </c>
       <c r="B44" t="n">
-        <v>0.1969141076959093</v>
+        <v>0.1969440466115558</v>
       </c>
       <c r="C44" t="n">
-        <v>0.9865883149461836</v>
+        <v>0.2110576125881977</v>
       </c>
       <c r="D44" t="inlineStr"/>
     </row>
@@ -963,10 +964,10 @@
         <v>0.5918367346938773</v>
       </c>
       <c r="B45" t="n">
-        <v>0.2966416639696795</v>
+        <v>0.2967044433590171</v>
       </c>
       <c r="C45" t="n">
-        <v>0.4095518314712586</v>
+        <v>0.8668717713773569</v>
       </c>
       <c r="D45" t="inlineStr"/>
     </row>
@@ -975,10 +976,10 @@
         <v>0.6326530612244896</v>
       </c>
       <c r="B46" t="n">
-        <v>0.4464542712486136</v>
+        <v>0.4465380766098946</v>
       </c>
       <c r="C46" t="n">
-        <v>0.1172517521102229</v>
+        <v>0.466596808368727</v>
       </c>
       <c r="D46" t="inlineStr"/>
     </row>
@@ -987,10 +988,10 @@
         <v>0.6734693877551019</v>
       </c>
       <c r="B47" t="n">
-        <v>0.6720392703184254</v>
+        <v>0.6720933397160392</v>
       </c>
       <c r="C47" t="n">
-        <v>0.1368589566044066</v>
+        <v>0.9460466873557939</v>
       </c>
       <c r="D47" t="inlineStr"/>
     </row>
@@ -999,10 +1000,10 @@
         <v>0.7142857142857142</v>
       </c>
       <c r="B48" t="n">
-        <v>1.011177317237043</v>
+        <v>1.011240650040471</v>
       </c>
       <c r="C48" t="n">
-        <v>0.6729078103291883</v>
+        <v>0.7987275619819455</v>
       </c>
       <c r="D48" t="inlineStr"/>
     </row>
@@ -1011,10 +1012,10 @@
         <v>0.7551020408163265</v>
       </c>
       <c r="B49" t="n">
-        <v>1.521174724340522</v>
+        <v>1.521273344023549</v>
       </c>
       <c r="C49" t="n">
-        <v>0.05706096372635006</v>
+        <v>0.3256512650068495</v>
       </c>
       <c r="D49" t="inlineStr"/>
     </row>
@@ -1023,10 +1024,10 @@
         <v>0.7959183673469385</v>
       </c>
       <c r="B50" t="n">
-        <v>2.288541958795224</v>
+        <v>2.288514247614526</v>
       </c>
       <c r="C50" t="n">
-        <v>0.8745720928882516</v>
+        <v>0.9172080040907298</v>
       </c>
       <c r="D50" t="inlineStr"/>
     </row>
@@ -1035,10 +1036,10 @@
         <v>0.8367346938775508</v>
       </c>
       <c r="B51" t="n">
-        <v>3.44252525053663</v>
+        <v>3.442597194972319</v>
       </c>
       <c r="C51" t="n">
-        <v>0.6584523877490425</v>
+        <v>0.497703320442907</v>
       </c>
       <c r="D51" t="inlineStr"/>
     </row>
@@ -1047,10 +1048,10 @@
         <v>0.8775510204081631</v>
       </c>
       <c r="B52" t="n">
-        <v>5.178193598563379</v>
+        <v>5.178137495097527</v>
       </c>
       <c r="C52" t="n">
-        <v>0.3530922863702315</v>
+        <v>0.7086856036855286</v>
       </c>
       <c r="D52" t="inlineStr"/>
     </row>
@@ -1059,10 +1060,10 @@
         <v>0.9183673469387754</v>
       </c>
       <c r="B53" t="n">
-        <v>7.788822868968189</v>
+        <v>7.788628957200799</v>
       </c>
       <c r="C53" t="n">
-        <v>0.7230498077314139</v>
+        <v>0.9376127031345048</v>
       </c>
       <c r="D53" t="inlineStr"/>
     </row>
@@ -1071,10 +1072,10 @@
         <v>0.9591836734693877</v>
       </c>
       <c r="B54" t="n">
-        <v>11.7149271313797</v>
+        <v>11.71488692814262</v>
       </c>
       <c r="C54" t="n">
-        <v>0.8830921622143103</v>
+        <v>0.3960782235023752</v>
       </c>
       <c r="D54" t="inlineStr"/>
     </row>
@@ -1083,10 +1084,10 @@
         <v>1</v>
       </c>
       <c r="B55" t="n">
-        <v>17.62043246550913</v>
+        <v>17.62038094307606</v>
       </c>
       <c r="C55" t="n">
-        <v>0.5777073684790215</v>
+        <v>0.4548618513818063</v>
       </c>
       <c r="D55" t="inlineStr"/>
     </row>
@@ -1113,6 +1114,42 @@
       <c r="B57" t="inlineStr"/>
       <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Fecha y hora inicio</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Isc</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-07-05 12:00:00</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>30.504</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
